--- a/artfynd/A 46272-2022 artfynd.xlsx
+++ b/artfynd/A 46272-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46272-2022 artfynd.xlsx
+++ b/artfynd/A 46272-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,138 +1053,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>111554621</v>
-      </c>
-      <c r="B5" t="n">
-        <v>99926</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1853</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Mosippa</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Pulsatilla vernalis</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Komstad, (Karlsberg 1100 m SO), Sm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>476954</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6360743</v>
-      </c>
-      <c r="S5" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Sävsjö</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Sävsjö</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>F-Säv-0041</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Jakob Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Jakob Wilhelmsson, Lars-Erik Eknäs</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46272-2022 artfynd.xlsx
+++ b/artfynd/A 46272-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2368337</v>
+        <v>484073</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219955</v>
+        <v>1853</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Karlsberg 1100 m SO, Sm</t>
+          <t>Komstad, (Karlsberg 1100 m SO), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476950.8751783952</v>
+        <v>476954</v>
       </c>
       <c r="R2" t="n">
-        <v>6360729.087159858</v>
+        <v>6360743</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,24 +738,24 @@
           <t>Sävsjö</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>F-Säv-0041</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-05-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1987-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Observatör: Birger Lindgren</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,30 +767,34 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gles tallskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>F-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via F-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>520678</v>
       </c>
       <c r="B3" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476950.8751783952</v>
+        <v>476951</v>
       </c>
       <c r="R3" t="n">
-        <v>6360729.087159858</v>
+        <v>6360729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +873,9 @@
           <t>2011-04-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-04-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -918,64 +907,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66486169</v>
+        <v>94803426</v>
       </c>
       <c r="B4" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1853</v>
+        <v>102980</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Komstad, (Karlsberg 1100 m SO), Sm</t>
+          <t>Näset, Komstad grusgrop, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476953.6541563318</v>
+        <v>476999</v>
       </c>
       <c r="R4" t="n">
-        <v>6360743.084465844</v>
+        <v>6360719</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,34 +978,14 @@
           <t>Sävsjö</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>F-Säv-0041</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-05-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-05-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Inga blommande plantor alls i år</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,19 +1000,112 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2368337</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Karlsberg 1100 m SO, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>476951</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6360729</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2011-05-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2011-05-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Leif Joakimsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46272-2022 artfynd.xlsx
+++ b/artfynd/A 46272-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/484073</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/520678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94803426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,8 +1126,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2368337</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>